--- a/data/dividends_info_20260531.xlsx
+++ b/data/dividends_info_20260531.xlsx
@@ -10245,316 +10245,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>AEFFE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>AEFFE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Adventure S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Cyberoo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>E-NOVIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>ECOSUNTEK S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>EXPERT.AI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Esprinet S.p.A.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>I GRANDI VIAGGI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Itway S.p.A.</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>MONDO TV FRANCE</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>MONDO TV S.p.A.</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>OPS ECOM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>OPS Italia S.p.A.</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Vivenda Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>